--- a/data/rules/migration_rules.xlsx
+++ b/data/rules/migration_rules.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -967,6 +967,1266 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ER-101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>card_no</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>card_tail</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MIN_LENGTH</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ER-102</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>full_name_raw</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>strip({full_name_raw})</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ER-103</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dob_fmt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DATE_FORMAT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>%d/%m/%Y</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ER-104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dob_iso</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dob_fmt</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DATE_TRANSFORM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>date_fmt(dob_iso, '%d/%m/%Y')</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ER-105</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>price_rounded</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NUMERIC_ROUND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>round(unit_price, 2)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ER-106</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>region_default</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DEFAULT_VALUE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifnull(region_code, 'GLOBAL')</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ER-107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>transform_lab,country_ref</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>LOOKUP</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>lookup(region)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ER-108</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>card_tail</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>REGEX</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>^\d{4}$</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ER-109</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>card_no</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>card_mask</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MASK</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>mask(card_no)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ER-110</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ssn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ssn_hash</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HASH</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>sha256(ssn)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ER-111</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pin_code</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>pin_enc</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ENCRYPTION</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>enc(pin_code)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ER-112</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pin_code</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>pin_enc</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DECRYPTION</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ER-113</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>card_no</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>card_tail</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SUBSTRING</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>substr(card_no, 12, 4)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ER-114</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>prod_ref</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>code_pref</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>prefix(prod_ref, 'AC-')</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ER-115</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>prod_ref</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>code_suff</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SUFFIX</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>suffix(prod_ref, '-ZZ')</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ER-116</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>flag_yx</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>flag_label</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CASE_WHEN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>case(flag_yx) when 'Y' then 'YES' when 'N' then 'NO' else 'OTHER'</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ER-117</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>card_mask</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CUSTOM_SQL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>card_mask LIKE '****%'</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ER-118</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>qty,pack_size</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>line_total</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CUSTOM_PYTHON</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>int(qty) * int(pack_size)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ER-119</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>prod_ref</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>prod_ref_up</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>UPPERCASE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>upper({prod_ref})</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ER-120</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>email_addr</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LOWERCASE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>lower({email_addr})</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ER-121</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>prod_ref,lab_id</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CONCAT</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>{prod_ref}|{lab_id}</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ER-122</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cust_tier</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>tier_label</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>map(cust_tier, tiers)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ER-123</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DIRECT_COMPARE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ER-124</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pin_code</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>pin_enc</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NULL_CHECK</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -978,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1105,6 +2365,57 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tiers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PLATINUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tiers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tiers</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SILVER</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/rules/migration_rules.xlsx
+++ b/data/rules/migration_rules.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2222,6 +2222,60 @@
         </is>
       </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ER-125</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>transform_lab,region_ref@country=ctry</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>transform_lab</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>LOOKUP</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>lookup(region)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>lab_id</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
